--- a/Antibiotic list_Indo.xlsx
+++ b/Antibiotic list_Indo.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/aling_nus_edu_sg/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NUS Dropbox\Xiangyuan Huang\github\BPOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{6EB8B688-369B-425B-9FC9-2E4BE64C0D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{529B0888-1785-4278-A49F-19471EA773E2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BD7F58-243A-4AF9-B987-4D4CA7715B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24048" yWindow="144" windowWidth="19200" windowHeight="16656" xr2:uid="{FFB9668C-6DB1-4F67-B5E1-E6FD1B5C8D84}"/>
+    <workbookView xWindow="-30828" yWindow="-4392" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{FFB9668C-6DB1-4F67-B5E1-E6FD1B5C8D84}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="36">
   <si>
     <t>Country</t>
   </si>
@@ -132,6 +133,51 @@
       </rPr>
       <t>4. Meropenem + Tigecycline</t>
     </r>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>Control mortality</t>
+  </si>
+  <si>
+    <t>Treatment mortality</t>
+  </si>
+  <si>
+    <t>BAT</t>
+  </si>
+  <si>
+    <t>polymyxin</t>
+  </si>
+  <si>
+    <t>Ceftazidime-avibactam</t>
+  </si>
+  <si>
+    <t>Test for</t>
+  </si>
+  <si>
+    <t>non-inferiority</t>
+  </si>
+  <si>
+    <t>superiority</t>
+  </si>
+  <si>
+    <t>N 
+(control + treatment)</t>
+  </si>
+  <si>
+    <t>N
+(poly+Ceft+BAT)</t>
+  </si>
+  <si>
+    <t>N*inflation factor/0.9</t>
+  </si>
+  <si>
+    <t>Proportion
+(treat+control)/total sample</t>
   </si>
 </sst>
 </file>
@@ -180,13 +226,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,17 +573,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2BB52A-7162-42BC-99A2-F59636E540FC}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -578,7 +629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -601,7 +652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -624,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -647,7 +698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -670,7 +721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -691,6 +742,170 @@
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F239AE-6C83-4C4F-8EE9-10840D991AEE}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.21875" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>321</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.72250000000000003</v>
+      </c>
+      <c r="H2">
+        <v>445</v>
+      </c>
+      <c r="I2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <v>267</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="H3">
+        <v>551</v>
+      </c>
+      <c r="I3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>3660</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.72250000000000003</v>
+      </c>
+      <c r="H4">
+        <v>5066</v>
+      </c>
+      <c r="I4">
+        <v>5779</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>3041</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="H5">
+        <v>6270</v>
+      </c>
+      <c r="I5">
+        <v>7153</v>
       </c>
     </row>
   </sheetData>
